--- a/schedule_optimizer/schedule_optimizer/Список_аудиторий_фейк_1x.xlsx
+++ b/schedule_optimizer/schedule_optimizer/Список_аудиторий_фейк_1x.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I210"/>
+  <dimension ref="A1:I209"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,86 +466,86 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ГУ598</t>
+          <t>ЛК651</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28</v>
+        <v>132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>ПК (14 шт), проектор</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>А451</t>
+          <t>А603</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>192</v>
+        <v>28</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>15 ПК, TV</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ЛК338</t>
+          <t>ПА-350</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Спортивный зал</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>70</v>
+        <v>400</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -557,42 +557,42 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ЛК-268</t>
+          <t>А228</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Ефимов А.Г.</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>10 ПК, TV</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -600,46 +600,40 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>А-722</t>
+          <t>ПА-846</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>200</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>ПК (10 шт), TV</t>
-        </is>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Институт экономики и финансов</t>
+          <t>Институт информационных систем</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>5</v>
-      </c>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ПА-339</t>
+          <t>А512</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -655,61 +649,61 @@
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Интеллектуальный пропаганда сустав экзамен.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Щукин Я.И.</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ПА-588</t>
+          <t>ЦИТ-533</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Дистанционное проведение</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Способ фонарик отметить смелый предоставить цель монета.</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Институт экономики и финансов</t>
-        </is>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ЦИТ-979</t>
+          <t>А705</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -718,7 +712,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -733,14 +727,12 @@
           <t>Поточный корпус</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>5</v>
-      </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>А-885</t>
+          <t>ГУ924</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -749,7 +741,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -761,26 +753,26 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ПА-241</t>
+          <t>ГУ633</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -789,28 +781,28 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Слать намерение смелый место.</t>
+          <t>17 ПК, TV</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Институт экономики и финансов</t>
+          <t>Институт информационных систем</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ЛК-674</t>
+          <t>ГУ840</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -819,29 +811,37 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>200</v>
+        <v>48</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Сынок ведь пятеро темнеть постоянный.</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>А-483</t>
+          <t>ЛК111</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -859,35 +859,37 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Носок ночь исследование поколение дремать карандаш труп ручей.</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Кошелев О.М.</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Процесс задержать что.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>А-710</t>
+          <t>ЦИТ-253</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -896,99 +898,107 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>15 ПК, TV</t>
+          <t>Моноблок (5 шт), проектор</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ГУ995</t>
+          <t>А338</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>200</v>
+        <v>24</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ПК (12 шт), проектор</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ЛК382</t>
+          <t>А-650</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Общего назначения</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Какой возможно затянуться горький головной исследование полюбить встать.</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Рябов Х.Л.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ПА-339</t>
+          <t>А-349</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>200</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -997,98 +1007,94 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>24 ПК, TV</t>
+          <t>Возникновение деньги головка.</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Институт маркетинга</t>
+          <t>Институт информационных систем</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ЛК382</t>
+          <t>ЦИТ-255</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Моноблок (12 шт), экран</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>А123</t>
+          <t>А512</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Общего назначения</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Светило выраженный гулять сверкать слишком школьный.</t>
-        </is>
-      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ЦИТ-292</t>
+          <t>ГУ-389</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1097,40 +1103,38 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Доставать указанный доставать возможно инструкция народ намерение.</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ЦИТ-317</t>
+          <t>А-582</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1139,28 +1143,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Академик металл интеллектуальный магазин встать набор.</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Кононова В.В.</t>
-        </is>
-      </c>
+          <t>Моноблок (6 шт), TV</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>8</v>
-      </c>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ЛК461</t>
+          <t>ЛК746</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1169,7 +1167,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1181,26 +1179,26 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ГУ609</t>
+          <t>А-612</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Спортивный зал</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>23</v>
+        <v>400</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1209,24 +1207,28 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>11 ПК, TV</t>
+          <t>Граница вперед смелый развернуться задрать.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>А-885</t>
+          <t>ГУ-389</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1235,7 +1237,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>176</v>
+        <v>100</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1243,45 +1245,35 @@
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Титов И.В.</t>
-        </is>
-      </c>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>2</v>
-      </c>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ЛК-948</t>
+          <t>ПА-500</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>ПК (12 шт), экран</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
@@ -1289,45 +1281,27 @@
           <t>Лабораторный корпус</t>
         </is>
       </c>
-      <c r="I25" t="n">
-        <v>6</v>
-      </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ЦИТ-386</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Учебная аудитория</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>50</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Государственный университет управления</t>
-        </is>
-      </c>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>2</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ЛК338</t>
+          <t>ЛК930</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1336,7 +1310,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1348,7 +1322,7 @@
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -1356,71 +1330,57 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ЦИТ-622</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Учебная аудитория</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>24</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Государственный университет управления</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Хотеть решение грустный правление военный построить что.</t>
-        </is>
-      </c>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ЛК595</t>
+          <t>ЦИТ-897</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Актовый зал</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Рот выражение коллектив коллектив.</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>А-483</t>
+          <t>ГУ924</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1429,7 +1389,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1437,21 +1397,23 @@
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Комиссаров Е.Л.</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>3</v>
-      </c>
+          <t>Лабораторный корпус</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ЦИТ-195</t>
+          <t>А-639</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1460,7 +1422,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1470,56 +1432,52 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Тарасова О.Ф.</t>
+          <t>Шашков Ф.Ф.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>1</v>
-      </c>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ГУ-483</t>
+          <t>ПА-846</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>16 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ПА-351</t>
+          <t>ЦИТ-470</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1528,7 +1486,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>60</v>
+        <v>192</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1537,20 +1495,24 @@
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ЛК-915</t>
+          <t>ЛК-802</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1559,7 +1521,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1568,59 +1530,55 @@
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ГУ896</t>
+          <t>А115</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>12 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ГУ995</t>
+          <t>А-612</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1629,91 +1587,99 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Другой художественный перебивать хлеб запретить миг команда рабочий.</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ЛК595</t>
+          <t>А228</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>22 ПК, TV</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ЦИТ-870</t>
+          <t>А771</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>192</v>
+        <v>28</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ПК (7 шт), TV</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>А-290</t>
+          <t>А-612</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1722,7 +1688,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1731,20 +1697,24 @@
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ГУ700</t>
+          <t>ЦИТ-470</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1753,7 +1723,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1762,7 +1732,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>19 ПК, TV</t>
+          <t>22 ПК, TV</t>
         </is>
       </c>
       <c r="F40" t="inlineStr"/>
@@ -1773,13 +1743,13 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ПА-742</t>
+          <t>А-910</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1788,7 +1758,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1797,24 +1767,20 @@
       </c>
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Институт экономики и финансов</t>
-        </is>
-      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ЛК-268</t>
+          <t>ЛК138</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1823,7 +1789,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1835,15 +1801,17 @@
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ПА-234</t>
+          <t>ГУ-115</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1852,7 +1820,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1861,24 +1829,20 @@
       </c>
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>А-885</t>
+          <t>ГУ-515</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1887,7 +1851,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1899,7 +1863,7 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -1907,51 +1871,51 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ПА-339</t>
+          <t>А-718</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>21 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ЦИТ-781</t>
+          <t>ГУ-574</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1960,37 +1924,31 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ПК (5 шт), TV</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Яковлева М.А.</t>
-        </is>
-      </c>
+          <t>Ставить торговля прежний интеллектуальный.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>5</v>
-      </c>
+          <t>Лабораторный корпус</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ГУ700</t>
+          <t>ГУ-437</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Общего назначения</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1998,25 +1956,21 @@
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Селезнев А.А.</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>А-221</t>
+          <t>ЛК-721</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2025,7 +1979,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2034,62 +1988,64 @@
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>А-483</t>
+          <t>А771</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Моноблок (6 шт), TV</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ГУ-198</t>
+          <t>ЦИТ-821</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>10</v>
+        <v>132</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2101,17 +2057,15 @@
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I50" t="n">
-        <v>6</v>
-      </c>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ЛК-517</t>
+          <t>ПА-835</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2120,7 +2074,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2132,57 +2086,57 @@
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ГУ-941</t>
+          <t>ПА-272</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>Моноблок (8 шт), TV</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ГУ-508</t>
+          <t>ЛК408</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Общего назначения</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -2194,17 +2148,17 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ЛК407</t>
+          <t>ЛК242</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2213,7 +2167,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2225,26 +2179,26 @@
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ЛК-174</t>
+          <t>ЛК-721</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Спортивный зал</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>400</v>
+        <v>70</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2252,34 +2206,30 @@
         </is>
       </c>
       <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Козлов К.Ф.</t>
-        </is>
-      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ЦИТ-781</t>
+          <t>А868</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2288,24 +2238,26 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Сопровождаться заработать степь похороны труп выраженный пасть заплакать.</t>
+          <t>Моноблок (14 шт), экран</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I56" t="n">
-        <v>2</v>
-      </c>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>А794</t>
+          <t>ЦИТ-140</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2314,7 +2266,7 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2323,42 +2275,44 @@
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>А-710</t>
+          <t>ГУ-115</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Моноблок (8 шт), экран</t>
+        </is>
+      </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Институт информационных систем</t>
+          <t>Институт маркетинга</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -2367,13 +2321,13 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ЦИТ-168</t>
+          <t>ЛК567</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2382,7 +2336,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2390,7 +2344,11 @@
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Лаврентьева Л.В.</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
@@ -2398,13 +2356,13 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>А-538</t>
+          <t>ГУ-744</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2413,7 +2371,7 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -2422,24 +2380,28 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Новый предоставить спорт зато заведение исследование.</t>
+          <t>Дрогнуть мальчишка еврейский постоянный.</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>Административный корпус</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ГУ-483</t>
+          <t>ГУ633</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2448,7 +2410,7 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>176</v>
+        <v>80</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2464,13 +2426,13 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>А-658</t>
+          <t>ПА-922</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2479,7 +2441,7 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>40</v>
+        <v>192</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2487,30 +2449,34 @@
         </is>
       </c>
       <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Галкин В.Б.</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>А341</t>
+          <t>ЛК549</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Спортивный зал</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>28</v>
+        <v>400</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2525,14 +2491,12 @@
           <t>Лабораторный корпус</t>
         </is>
       </c>
-      <c r="I63" t="n">
-        <v>8</v>
-      </c>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ЦИТ-757</t>
+          <t>ГУ-618</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2541,7 +2505,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2549,32 +2513,30 @@
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Белозерова К.Ф.</t>
-        </is>
-      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>А302</t>
+          <t>ПА-716</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Спортивный зал</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2583,24 +2545,18 @@
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I65" t="n">
-        <v>8</v>
-      </c>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ЦИТ-525</t>
+          <t>ЛК237</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2609,7 +2565,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>132</v>
+        <v>28</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2621,68 +2577,72 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ПА-351</t>
+          <t>ГУ-618</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>ПК (5 шт), TV</t>
-        </is>
-      </c>
+      <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ПА-372</t>
+          <t>ЛК179</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ПК (9 шт), TV</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
@@ -2690,14 +2650,12 @@
           <t>Поточный корпус</t>
         </is>
       </c>
-      <c r="I68" t="n">
-        <v>2</v>
-      </c>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>А-929</t>
+          <t>ПА-403</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2706,7 +2664,7 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>192</v>
+        <v>24</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2718,61 +2676,57 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ЛК841</t>
+          <t>А-349</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>14 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ЛК841</t>
+          <t>А-826</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -2781,67 +2735,37 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20 ПК, TV</t>
+          <t>Моноблок (8 шт), экран</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
-      <c r="I71" t="n">
-        <v>6</v>
-      </c>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>А-160</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Компьютерный класс</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>10</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Государственный университет управления</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>13 ПК, TV</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Мишина И.А.</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="I72" t="n">
-        <v>6</v>
-      </c>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr"/>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ЛК595</t>
+          <t>ЦИТ-724</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2850,38 +2774,46 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>36</v>
+        <v>200</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Непривычный степь военный степь низкий приятель выбирать.</t>
+        </is>
+      </c>
       <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ЦИТ-609</t>
+          <t>ЛК-315</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Общего назначения</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -2893,17 +2825,17 @@
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ГУ-508</t>
+          <t>А-741</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2912,7 +2844,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2924,7 +2856,7 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -2934,7 +2866,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>А-160</t>
+          <t>ГУ-437</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2943,114 +2875,130 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>200</v>
+        <v>32</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>Зеленый смелый инструкция коробка подземный смертельный.</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I76" t="n">
-        <v>5</v>
-      </c>
+          <t>Лабораторный корпус</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>А253</t>
+          <t>А-409</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Спортивный зал</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>400</v>
+        <v>20</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Моноблок (12 шт), TV</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I77" t="n">
-        <v>7</v>
-      </c>
+          <t>Лабораторный корпус</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>А-849</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Компьютерный класс</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>12</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Государственный университет управления</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>10 ПК, TV</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Мельников Т.Т.</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
           <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ЦИТ-168</t>
+          <t>А368</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Дистанционное проведение</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>1000</v>
+        <v>176</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>Чем ведь сынок пропасть.</t>
-        </is>
-      </c>
+      <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>А-554</t>
+          <t>ЛК-919</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3059,72 +3007,68 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Наслаждение пропадать сынок.</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>Административный корпус</t>
         </is>
       </c>
-      <c r="I80" t="n">
-        <v>3</v>
-      </c>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>А-489</t>
+          <t>ЛК-189</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>ПК (13 шт), TV</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Соловьев С.В.</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+          <t>Якушева П.В.</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
       <c r="H81" t="inlineStr">
         <is>
           <t>Спортивный комплекс</t>
         </is>
       </c>
-      <c r="I81" t="n">
-        <v>8</v>
-      </c>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ЦИТ-422</t>
+          <t>ПА-575</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3133,7 +3077,7 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -3142,24 +3086,20 @@
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ЦИТ-610</t>
+          <t>ПА-220</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3168,7 +3108,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -3177,26 +3117,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Появление пространство космос.</t>
+          <t>Господь табак подробность плясать термин пространство дальний.</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>А120</t>
+          <t>ГУ-415</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3205,7 +3143,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>192</v>
+        <v>30</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -3214,82 +3152,78 @@
       </c>
       <c r="E84" t="inlineStr"/>
       <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>А-722</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Учебная аудитория</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>32</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Государственный университет управления</t>
-        </is>
-      </c>
+          <t>Лабораторный корпус</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr"/>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I85" t="n">
-        <v>2</v>
-      </c>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ПА-372</t>
+          <t>ПА-672</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>12 ПК, TV</t>
+        </is>
+      </c>
       <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ГУ-382</t>
+          <t>ПА-220</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3298,7 +3232,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -3310,17 +3244,17 @@
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>А-963</t>
+          <t>ПА-524</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3329,7 +3263,7 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -3338,22 +3272,20 @@
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
           <t>Главный учебный корпус</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ЦИТ-870</t>
+          <t>ПА-922</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3362,7 +3294,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -3374,71 +3306,71 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ЛК722</t>
+          <t>А-718</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>14 ПК, TV</t>
+        </is>
+      </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I90" t="n">
-        <v>3</v>
-      </c>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ПА-103</t>
+          <t>А946</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>22 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -3446,7 +3378,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ГУ182</t>
+          <t>ГУ-515</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3455,7 +3387,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -3467,17 +3399,17 @@
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ЛК-567</t>
+          <t>ЛК374</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3486,7 +3418,7 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -3498,15 +3430,17 @@
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ЛК407</t>
+          <t>ПА-224</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3515,7 +3449,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -3523,28 +3457,34 @@
         </is>
       </c>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Котов Г.И.</t>
+        </is>
+      </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
           <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ЦИТ-781</t>
+          <t>А-849</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Спортивный зал</t>
+          <t>Общего назначения</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>400</v>
+        <v>10</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -3553,20 +3493,24 @@
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ГУ-483</t>
+          <t>ЦИТ-533</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3575,7 +3519,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -3584,57 +3528,59 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>25 ПК, TV</t>
+          <t>18 ПК, TV</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>А-563</t>
+          <t>ПА-220</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>25 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E97" t="inlineStr"/>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ЦИТ-195</t>
+          <t>ПА-124</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3643,7 +3589,7 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -3652,14 +3598,14 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>25 ПК, TV</t>
+          <t>20 ПК, TV</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I98" t="n">
@@ -3669,16 +3615,16 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ЛК-153</t>
+          <t>ГУ351</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -3687,37 +3633,39 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>ПК (9 шт), экран</t>
+          <t>Нож куча тюрьма похороны рассуждение рис.</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Миронова Ф.В.</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr"/>
+          <t>Ларионова И.Ф.</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H99" t="inlineStr">
         <is>
           <t>Поточный корпус</t>
         </is>
       </c>
-      <c r="I99" t="n">
-        <v>1</v>
-      </c>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ПА-799</t>
+          <t>А946</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Общего назначения</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -3726,24 +3674,20 @@
       </c>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ПА-372</t>
+          <t>ЛК780</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3752,7 +3696,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -3768,13 +3712,13 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>А341</t>
+          <t>ЛК-942</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3783,7 +3727,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -3792,80 +3736,54 @@
       </c>
       <c r="E102" t="inlineStr"/>
       <c r="F102" t="inlineStr"/>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+      <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
-      <c r="I102" t="n">
-        <v>3</v>
-      </c>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ЦИТ-610</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Учебная аудитория</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>20</v>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Государственный университет управления</t>
-        </is>
-      </c>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr"/>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
-      <c r="I103" t="n">
-        <v>8</v>
-      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ГУ688</t>
+          <t>А-910</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Бобылев Р.А.</t>
-        </is>
-      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>20 ПК, TV</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
@@ -3879,42 +3797,38 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ЛК-300</t>
+          <t>ГУ780</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>28</v>
+        <v>200</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>ПК (13 шт), проектор</t>
-        </is>
-      </c>
+      <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ГУ181</t>
+          <t>А-674</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3923,7 +3837,7 @@
         </is>
       </c>
       <c r="C106" t="n">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -3931,25 +3845,25 @@
         </is>
       </c>
       <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Меркушев В.Ю.</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ЛК461</t>
+          <t>А368</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3958,7 +3872,7 @@
         </is>
       </c>
       <c r="C107" t="n">
-        <v>24</v>
+        <v>200</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -3973,60 +3887,82 @@
           <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
-      <c r="I107" t="n">
-        <v>3</v>
-      </c>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr"/>
-      <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" t="inlineStr"/>
+          <t>ПА-500</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Учебная аудитория</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>26</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Государственный университет управления</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Вперед сбросить прелесть порода постоянный пропадать.</t>
+        </is>
+      </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
-      <c r="I108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ЛК382</t>
+          <t>ЦИТ-813</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>24 ПК, TV</t>
+        </is>
+      </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
@@ -4041,7 +3977,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ЛК821</t>
+          <t>А603</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4050,7 +3986,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>80</v>
+        <v>36</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -4062,38 +3998,46 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ГУ688</t>
+          <t>ЛК857</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>17 ПК, TV</t>
+        </is>
+      </c>
       <c r="F112" t="inlineStr"/>
-      <c r="G112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -4101,16 +4045,16 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ГУ-382</t>
+          <t>ЛК903</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Спортивный зал</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>192</v>
+        <v>400</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -4119,33 +4063,29 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Опасность термин слишком кожа зеленый возникновение бак.</t>
+          <t>Похороны неожиданный некоторый что приятель.</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+      <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ЛК-915</t>
+          <t>ПА-716</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -4158,28 +4098,24 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>22 ПК, TV</t>
+          <t>Моноблок (14 шт), проектор</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ЦИТ-139</t>
+          <t>ГУ-574</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4188,7 +4124,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>60</v>
+        <v>200</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -4200,83 +4136,85 @@
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I115" t="n">
-        <v>4</v>
-      </c>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ГУ-128</t>
+          <t>ЦИТ-228</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>18</v>
+        <v>200</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Моноблок (14 шт), экран</t>
-        </is>
-      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H116" t="inlineStr">
         <is>
           <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ГУ381</t>
+          <t>ГУ-846</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>132</v>
+        <v>16</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Моноблок (8 шт), TV</t>
+        </is>
+      </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>А-710</t>
+          <t>А-322</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4294,57 +4232,55 @@
       </c>
       <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+      <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I118" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ПА-228</t>
+          <t>ЛК111</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>10 ПК, TV</t>
+        </is>
+      </c>
       <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+      <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I119" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ЛК208</t>
+          <t>ЦИТ-634</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4353,73 +4289,75 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Механический граница висеть стакан крутой спешить.</t>
-        </is>
-      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H120" t="inlineStr">
         <is>
           <t>Административный корпус</t>
         </is>
       </c>
-      <c r="I120" t="n">
-        <v>6</v>
-      </c>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ГУ-819</t>
+          <t>ПА-835</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>ПК (9 шт), экран</t>
+        </is>
+      </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ЛК407</t>
+          <t>ПА-500</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -4431,17 +4369,17 @@
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ГУ381</t>
+          <t>ЦИТ-533</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4450,7 +4388,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>200</v>
+        <v>28</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -4459,84 +4397,82 @@
       </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
-      <c r="I123" t="n">
-        <v>3</v>
-      </c>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>А-419</t>
+          <t>ГУ-415</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Общего назначения</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Засунуть низкий вчера.</t>
+        </is>
+      </c>
       <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ГУ-382</t>
+          <t>ПА-701</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Общего назначения</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>18 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Институт маркетинга</t>
+          <t>Институт экономики и финансов</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I125" t="n">
@@ -4546,16 +4482,16 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ЛК-268</t>
+          <t>А600</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -4564,48 +4500,70 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>20 ПК, TV</t>
+          <t>Функция столетие вскакивать тревога передо бабочка.</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr"/>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr"/>
+          <t>ЛК790</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Компьютерный класс</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>17</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Государственный университет управления</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>13 ПК, TV</t>
+        </is>
+      </c>
       <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Административный корпус</t>
+        </is>
+      </c>
       <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ГУ-440</t>
+          <t>ПА-220</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Дистанционное проведение</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -4613,34 +4571,28 @@
         </is>
       </c>
       <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Потапов В.Л.</t>
-        </is>
-      </c>
+      <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I128" t="n">
-        <v>1</v>
-      </c>
+          <t>Лабораторный корпус</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>А-722</t>
+          <t>А-639</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -4648,30 +4600,34 @@
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Яковлев М.А.</t>
+        </is>
+      </c>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>А-793</t>
+          <t>А-309</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Спортивный зал</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>176</v>
+        <v>400</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -4683,17 +4639,17 @@
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>А341</t>
+          <t>ЛК990</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4702,40 +4658,42 @@
         </is>
       </c>
       <c r="C131" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Терапия девка вскинуть реклама исполнять написать.</t>
-        </is>
-      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="I131" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ЦИТ-757</t>
+          <t>ЛК790</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Дистанционное проведение</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -4747,26 +4705,26 @@
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ПА-799</t>
+          <t>ГУ840</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -4775,10 +4733,14 @@
       </c>
       <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -4786,27 +4748,23 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>А-538</t>
+          <t>ЦИТ-253</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>18</v>
+        <v>192</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Деньги разнообразный девка затянуться демократия сходить кпсс.</t>
-        </is>
-      </c>
+      <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
@@ -4815,70 +4773,88 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ПА-339</t>
+          <t>ПА-922</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>14 ПК, TV</t>
+        </is>
+      </c>
       <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I135" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr"/>
-      <c r="C136" t="inlineStr"/>
-      <c r="D136" t="inlineStr"/>
+          <t>А413</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Учебная аудитория</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>28</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Государственный университет управления</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I136" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>А-710</t>
+          <t>ЛК242</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Спортивный зал</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>400</v>
+        <v>176</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -4890,17 +4866,15 @@
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
-      <c r="I137" t="n">
-        <v>5</v>
-      </c>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ЦИТ-783</t>
+          <t>ГУ209</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4909,7 +4883,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -4918,29 +4892,31 @@
       </c>
       <c r="E138" t="inlineStr"/>
       <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I138" t="n">
-        <v>7</v>
-      </c>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>А341</t>
+          <t>ПА-524</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Актовый зал</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -4949,18 +4925,24 @@
       </c>
       <c r="E139" t="inlineStr"/>
       <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr"/>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I139" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ЦИТ-845</t>
+          <t>ЛК796</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4969,7 +4951,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -4981,26 +4963,26 @@
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ЛК841</t>
+          <t>А644</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Актовый зал</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>1000</v>
+        <v>176</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -5012,17 +4994,17 @@
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I141" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>А-343</t>
+          <t>ПА-922</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5031,7 +5013,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>80</v>
+        <v>192</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -5039,34 +5021,30 @@
         </is>
       </c>
       <c r="E142" t="inlineStr"/>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Соловьев А.Ю.</t>
-        </is>
-      </c>
+      <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ПА-243</t>
+          <t>ЦИТ-575</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Общего назначения</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -5082,38 +5060,38 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ГУ688</t>
+          <t>ГУ924</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Моноблок (10 шт), проектор</t>
-        </is>
-      </c>
+      <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I144" t="n">
@@ -5123,7 +5101,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ЛК-915</t>
+          <t>ЛК374</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5132,33 +5110,29 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>32</v>
+        <v>200</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Горький выражение изба за поздравлять пространство.</t>
-        </is>
-      </c>
+      <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>А302</t>
+          <t>А314</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5167,7 +5141,7 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -5189,22 +5163,36 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr"/>
-      <c r="C147" t="inlineStr"/>
-      <c r="D147" t="inlineStr"/>
+          <t>ПА-102</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Актовый зал</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>800</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Государственный университет управления</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr"/>
-      <c r="H147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Административный корпус</t>
+        </is>
+      </c>
       <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ГУ688</t>
+          <t>ЛК990</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5213,7 +5201,7 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>24</v>
+        <v>132</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -5225,46 +5213,52 @@
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ЦИТ-386</t>
+          <t>ГУ209</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>200</v>
+        <v>28</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>23 ПК, TV</t>
+        </is>
+      </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr"/>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I149" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ЛК841</t>
+          <t>ПА-412</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5273,7 +5267,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>26</v>
+        <v>100</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -5282,24 +5276,20 @@
       </c>
       <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>Институт экономики и финансов</t>
-        </is>
-      </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ЛК841</t>
+          <t>А-910</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5308,7 +5298,7 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -5323,31 +5313,29 @@
       <c r="F151" t="inlineStr"/>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Институт маркетинга</t>
+          <t>Институт управления</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="I151" t="n">
-        <v>7</v>
-      </c>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ЛК-517</t>
+          <t>ПА-124</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -5356,7 +5344,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Граница необычный бровь помимо лететь.</t>
+          <t>21 ПК, TV</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
@@ -5367,44 +5355,48 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>А324</t>
+          <t>ЦИТ-821</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>60</v>
+        <v>18</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>15 ПК, TV</t>
+        </is>
+      </c>
       <c r="F153" t="inlineStr"/>
       <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I153" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ЦИТ-757</t>
+          <t>ПА-922</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5413,7 +5405,7 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>192</v>
+        <v>28</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -5422,11 +5414,7 @@
       </c>
       <c r="E154" t="inlineStr"/>
       <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>Институт экономики и финансов</t>
-        </is>
-      </c>
+      <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
           <t>Цифровой корпус ГУУ</t>
@@ -5439,7 +5427,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ЛК511</t>
+          <t>ЛК378</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5448,7 +5436,7 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>192</v>
+        <v>32</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -5470,58 +5458,60 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>А-160</t>
+          <t>А-650</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>24 ПК, TV</t>
+        </is>
+      </c>
       <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I156" t="n">
-        <v>2</v>
-      </c>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ГУ-941</t>
+          <t>ЦИТ-255</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>ПК (8 шт), экран</t>
+        </is>
+      </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
@@ -5534,7 +5524,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ПА-339</t>
+          <t>ГУ-389</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5543,7 +5533,7 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -5552,27 +5542,33 @@
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="I158" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ЛК595</t>
+          <t>А-805</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Общего назначения</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>132</v>
+        <v>16</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -5581,49 +5577,59 @@
       </c>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ЛК-940</t>
+          <t>ГУ-846</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>10 ПК, TV</t>
+        </is>
+      </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I160" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ГУ-508</t>
+          <t>ПА-846</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5632,7 +5638,7 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -5644,59 +5650,55 @@
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I161" t="n">
-        <v>5</v>
-      </c>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>А120</t>
+          <t>ПА-102</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>ПК (13 шт), экран</t>
-        </is>
-      </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I162" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ГУ381</t>
+          <t>ГУ-846</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -5705,90 +5707,94 @@
       </c>
       <c r="E163" t="inlineStr"/>
       <c r="F163" t="inlineStr"/>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>Институт экономики и финансов</t>
-        </is>
-      </c>
+      <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr"/>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I163" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ЛК-915</t>
+          <t>ЛК242</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>11 ПК, TV</t>
+        </is>
+      </c>
       <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr"/>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I164" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ГУ826</t>
+          <t>ПА-224</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>ПК (14 шт), экран</t>
+        </is>
+      </c>
       <c r="F165" t="inlineStr"/>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Институт экономики и финансов</t>
+          <t>Институт маркетинга</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ГУ370</t>
+          <t>ЦИТ-491</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5797,7 +5803,7 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -5813,17 +5819,17 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I166" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ЦИТ-292</t>
+          <t>А644</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5832,7 +5838,7 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -5844,50 +5850,32 @@
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="I167" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>А-554</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Компьютерный класс</t>
-        </is>
-      </c>
-      <c r="C168" t="n">
-        <v>17</v>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>Государственный университет управления</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>23 ПК, TV</t>
-        </is>
-      </c>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I168" t="n">
-        <v>7</v>
-      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ЦИТ-422</t>
+          <t>ПА-370</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5915,14 +5903,12 @@
           <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
-      <c r="I169" t="n">
-        <v>5</v>
-      </c>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>ГУ523</t>
+          <t>А-718</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5931,7 +5917,7 @@
         </is>
       </c>
       <c r="C170" t="n">
-        <v>132</v>
+        <v>30</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -5939,7 +5925,11 @@
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr"/>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Панова М.Ю.</t>
+        </is>
+      </c>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
@@ -5947,13 +5937,13 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>А223</t>
+          <t>ПА-922</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5962,7 +5952,7 @@
         </is>
       </c>
       <c r="C171" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -5974,17 +5964,15 @@
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="I171" t="n">
-        <v>4</v>
-      </c>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>А-963</t>
+          <t>ЛК374</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5993,7 +5981,7 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>70</v>
+        <v>132</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -6002,20 +5990,22 @@
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I172" t="n">
-        <v>8</v>
-      </c>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ЛК722</t>
+          <t>А314</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -6024,7 +6014,7 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -6036,67 +6026,83 @@
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I173" t="n">
-        <v>2</v>
-      </c>
+          <t>Лабораторный корпус</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr"/>
-      <c r="C174" t="inlineStr"/>
-      <c r="D174" t="inlineStr"/>
+          <t>ГУ780</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Учебная аудитория</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>30</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Государственный университет управления</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr"/>
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ГУ700</t>
+          <t>ГУ-415</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>176</v>
+        <v>20</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>16 ПК, TV</t>
+        </is>
+      </c>
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Институт маркетинга</t>
+          <t>Институт информационных систем</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I175" t="n">
-        <v>5</v>
-      </c>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ГУ-203</t>
+          <t>ПА-716</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -6105,7 +6111,7 @@
         </is>
       </c>
       <c r="C176" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -6117,26 +6123,26 @@
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I176" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>А123</t>
+          <t>ПА-524</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Общего назначения</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -6144,19 +6150,25 @@
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Фомина Л.А.</t>
+        </is>
+      </c>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
           <t>Спортивный комплекс</t>
         </is>
       </c>
-      <c r="I177" t="inlineStr"/>
+      <c r="I177" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ГУ-333</t>
+          <t>ГУ-115</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -6165,7 +6177,7 @@
         </is>
       </c>
       <c r="C178" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -6177,17 +6189,17 @@
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I178" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>А-221</t>
+          <t>ЛК408</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -6196,7 +6208,7 @@
         </is>
       </c>
       <c r="C179" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -6204,19 +6216,25 @@
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Ковалева Э.Р.</t>
+        </is>
+      </c>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I179" t="inlineStr"/>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I179" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ЛК-915</t>
+          <t>ЛК242</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6225,7 +6243,7 @@
         </is>
       </c>
       <c r="C180" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -6234,24 +6252,24 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>24 ПК, TV</t>
+          <t>22 ПК, TV</t>
         </is>
       </c>
       <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I180" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ЛК-296</t>
+          <t>ЛК790</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -6260,7 +6278,7 @@
         </is>
       </c>
       <c r="C181" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -6269,20 +6287,24 @@
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I181" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ЛК-948</t>
+          <t>ЦИТ-897</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6291,7 +6313,7 @@
         </is>
       </c>
       <c r="C182" t="n">
-        <v>50</v>
+        <v>192</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -6303,38 +6325,50 @@
       <c r="G182" t="inlineStr"/>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I182" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>А-419</t>
+          <t>ГУ351</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C183" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr"/>
-      <c r="F183" t="inlineStr"/>
-      <c r="G183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>ПК (5 шт), проектор</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Тихонова Т.С.</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I183" t="n">
@@ -6344,7 +6378,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>А-658</t>
+          <t>ЛК179</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6353,7 +6387,7 @@
         </is>
       </c>
       <c r="C184" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -6362,7 +6396,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Моноблок (10 шт), экран</t>
+          <t>ПК (8 шт), проектор</t>
         </is>
       </c>
       <c r="F184" t="inlineStr"/>
@@ -6373,13 +6407,13 @@
         </is>
       </c>
       <c r="I184" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ПА-103</t>
+          <t>ЦИТ-126</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6388,7 +6422,7 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>24</v>
+        <v>132</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -6397,24 +6431,18 @@
       </c>
       <c r="E185" t="inlineStr"/>
       <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I185" t="n">
-        <v>8</v>
-      </c>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>А-419</t>
+          <t>ЛК138</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6423,7 +6451,7 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -6435,17 +6463,17 @@
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>А451</t>
+          <t>А-978</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6454,7 +6482,7 @@
         </is>
       </c>
       <c r="C187" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -6466,17 +6494,17 @@
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I187" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ЛК407</t>
+          <t>ГУ667</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6485,38 +6513,42 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>42</v>
+        <v>132</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Успокоиться адвокат издали армейский бегать.</t>
+        </is>
+      </c>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I188" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ЛК841</t>
+          <t>ГУ-958</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -6525,24 +6557,28 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Моноблок (8 шт), проектор</t>
+          <t>12 ПК, TV</t>
         </is>
       </c>
       <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I189" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ПА-243</t>
+          <t>А-718</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6551,7 +6587,7 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>60</v>
+        <v>176</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -6560,18 +6596,24 @@
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I190" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ЦИТ-857</t>
+          <t>ЦИТ-253</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6580,50 +6622,58 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Актриса один одиннадцать костер.</t>
+        </is>
+      </c>
       <c r="F191" t="inlineStr"/>
       <c r="G191" t="inlineStr"/>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ЦИТ-615</t>
+          <t>ЦИТ-634</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>13 ПК, TV</t>
+        </is>
+      </c>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I192" t="n">
@@ -6633,7 +6683,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ЦИТ-168</t>
+          <t>А946</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6642,7 +6692,7 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -6651,24 +6701,18 @@
       </c>
       <c r="E193" t="inlineStr"/>
       <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I193" t="n">
-        <v>6</v>
-      </c>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ГУ802</t>
+          <t>ЛК865</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6677,7 +6721,7 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>38</v>
+        <v>176</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -6689,17 +6733,17 @@
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I194" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ЦИТ-610</t>
+          <t>ЛК780</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6708,7 +6752,7 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>20</v>
+        <v>176</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -6717,24 +6761,18 @@
       </c>
       <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr">
         <is>
           <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
-      <c r="I195" t="n">
-        <v>6</v>
-      </c>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ЛК461</t>
+          <t>ЛК-988</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6743,7 +6781,7 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -6755,52 +6793,44 @@
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I196" t="n">
-        <v>7</v>
-      </c>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ЛК-708</t>
+          <t>А644</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C197" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>18 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I197" t="n">
-        <v>7</v>
-      </c>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>А-722</t>
+          <t>А-309</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6809,7 +6839,7 @@
         </is>
       </c>
       <c r="C198" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -6817,12 +6847,12 @@
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>Титова Л.Д.</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H198" t="inlineStr">
         <is>
           <t>Лабораторный корпус</t>
@@ -6833,32 +6863,32 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ГУ-136</t>
+          <t>ГУ359</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Актовый зал</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>5000</v>
+        <v>16</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>22 ПК, TV</t>
+        </is>
+      </c>
       <c r="F199" t="inlineStr"/>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I199" t="n">
@@ -6868,125 +6898,139 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr"/>
-      <c r="C200" t="inlineStr"/>
-      <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr"/>
+          <t>ГУ860</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Компьютерный класс</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>21</v>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Государственный университет управления</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>20 ПК, TV</t>
+        </is>
+      </c>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr"/>
-      <c r="H200" t="inlineStr"/>
-      <c r="I200" t="inlineStr"/>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="I200" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ЦИТ-695</t>
+          <t>ПА-309</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C201" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>22 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ГУ370</t>
+          <t>А420</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>22 ПК, TV</t>
+        </is>
+      </c>
       <c r="F202" t="inlineStr"/>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ГУ-198</t>
+          <t>А314</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Общего назначения</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>19 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr"/>
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I203" t="inlineStr"/>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I203" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ЦИТ-615</t>
+          <t>ЛК237</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6995,7 +7039,7 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -7003,54 +7047,60 @@
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr"/>
-      <c r="G204" t="inlineStr"/>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Тимофеева Е.О.</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="I204" t="inlineStr"/>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I204" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>А630</t>
+          <t>ГУ962</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C205" t="n">
-        <v>16</v>
+        <v>60</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>Моноблок (6 шт), экран</t>
-        </is>
-      </c>
+      <c r="E205" t="inlineStr"/>
       <c r="F205" t="inlineStr"/>
       <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I205" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ГУ-941</t>
+          <t>А-349</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -7059,7 +7109,7 @@
         </is>
       </c>
       <c r="C206" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -7074,23 +7124,21 @@
           <t>Главный учебный корпус</t>
         </is>
       </c>
-      <c r="I206" t="n">
-        <v>6</v>
-      </c>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>ЦИТ-727</t>
+          <t>А420</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Актовый зал</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C207" t="n">
-        <v>5000</v>
+        <v>60</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -7101,22 +7149,22 @@
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Институт экономики и финансов</t>
+          <t>Институт управления</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I207" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ЦИТ-525</t>
+          <t>ПА-148</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -7132,31 +7180,35 @@
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Наступать космос заплакать развитый.</t>
+        </is>
+      </c>
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I208" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ГУ-203</t>
+          <t>ЦИТ-575</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C209" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -7165,47 +7217,18 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Пламя деньги намерение ребятишки выразить смелый затянуться.</t>
+          <t>19 ПК, TV</t>
         </is>
       </c>
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr"/>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>А341</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Учебная аудитория</t>
-        </is>
-      </c>
-      <c r="C210" t="n">
-        <v>24</v>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>Государственный университет управления</t>
-        </is>
-      </c>
-      <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr"/>
-      <c r="G210" t="inlineStr"/>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I210" t="n">
-        <v>2</v>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I209" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/schedule_optimizer/schedule_optimizer/Список_аудиторий_фейк_1x.xlsx
+++ b/schedule_optimizer/schedule_optimizer/Список_аудиторий_фейк_1x.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I209"/>
+  <dimension ref="A1:I206"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ЛК651</t>
+          <t>ГУ169</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -475,23 +475,27 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>132</v>
+        <v>38</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Близко сопровождаться вскинуть мотоцикл провинция.</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Институт информационных систем</t>
+          <t>Институт управления</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -501,51 +505,47 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>А603</t>
+          <t>ЛК374</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Спортивный зал</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28</v>
+        <v>400</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>15 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ПА-350</t>
+          <t>ЛК-459</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Спортивный зал</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -557,50 +557,48 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>А228</t>
+          <t>ПА-721</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>10 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ПА-846</t>
+          <t>ПА-809</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -609,7 +607,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -618,22 +616,20 @@
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>А512</t>
+          <t>ЦИТ-252</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -642,37 +638,29 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Интеллектуальный пропаганда сустав экзамен.</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Щукин Я.И.</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ЦИТ-533</t>
+          <t>А-653</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -681,29 +669,37 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Слишком выражаться при сходить.</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>А705</t>
+          <t>ЦИТ-247</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -712,7 +708,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -721,18 +717,24 @@
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ГУ924</t>
+          <t>ГУ-638</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -753,104 +755,70 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1</v>
-      </c>
+          <t>Лабораторный корпус</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ГУ633</t>
+          <t>ПА-836</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>17 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ГУ840</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Учебная аудитория</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>48</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Государственный университет управления</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Сынок ведь пятеро темнеть постоянный.</t>
-        </is>
-      </c>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Институт экономики и финансов</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ЛК111</t>
+          <t>ГУ354</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -859,107 +827,101 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Процесс задержать что.</t>
+          <t>ПК (11 шт), TV</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>7</v>
-      </c>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ЦИТ-253</t>
+          <t>А-653</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Моноблок (5 шт), проектор</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>А338</t>
+          <t>ПА-580</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>ПК (12 шт), проектор</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>А-650</t>
+          <t>ГУ260</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -967,29 +929,19 @@
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Рябов Х.Л.</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>8</v>
-      </c>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>А-349</t>
+          <t>ПА-188</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -998,37 +950,33 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Возникновение деньги головка.</t>
-        </is>
-      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Институт информационных систем</t>
+          <t>Институт управления</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ЦИТ-255</t>
+          <t>ПА-728</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1037,7 +985,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1049,52 +997,54 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>5</v>
-      </c>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>А512</t>
+          <t>ПА-193</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>12 ПК, TV</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Институт экономики и финансов</t>
+          <t>Институт маркетинга</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ГУ-389</t>
+          <t>А944</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1103,7 +1053,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1115,26 +1065,26 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>А-582</t>
+          <t>ГУ-511</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1143,43 +1093,53 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Моноблок (6 шт), TV</t>
+          <t>10 ПК, TV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ЛК746</t>
+          <t>ЛК784</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>10 ПК, TV</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1189,7 +1149,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>А-612</t>
+          <t>А-924</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1205,59 +1165,61 @@
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Граница вперед смелый развернуться задрать.</t>
-        </is>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ГУ-389</t>
+          <t>А380</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Моноблок (15 шт), проектор</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Кондратьева Г.Х.</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ПА-500</t>
+          <t>ЛК677</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1266,7 +1228,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1278,46 +1240,72 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+          <t>ЛК592</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Компьютерный класс</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>16</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Государственный университет управления</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>23 ПК, TV</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ЛК930</t>
+          <t>ГУ354</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>25 ПК, TV</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
@@ -1325,71 +1313,83 @@
           <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+          <t>ЛК-404</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Учебная аудитория</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>176</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Государственный университет управления</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Административный корпус</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ЦИТ-897</t>
+          <t>ГУ400</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Актовый зал</t>
+          <t>Дистанционное проведение</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Рот выражение коллектив коллектив.</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ГУ924</t>
+          <t>ЛК-449</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Актовый зал</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>40</v>
+        <v>5000</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1397,23 +1397,21 @@
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Комиссаров Е.Л.</t>
-        </is>
-      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>А-639</t>
+          <t>А-284</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1422,7 +1420,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>176</v>
+        <v>24</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1430,23 +1428,25 @@
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Шашков Ф.Ф.</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ПА-846</t>
+          <t>ЛК374</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1455,7 +1455,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>38</v>
+        <v>132</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1467,52 +1467,52 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ЦИТ-470</t>
+          <t>А-813</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>192</v>
+        <v>28</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Моноблок (14 шт), экран</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Институт экономики и финансов</t>
-        </is>
-      </c>
+      <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
           <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ЛК-802</t>
+          <t>ЛК-389</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1521,7 +1521,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1530,24 +1530,18 @@
       </c>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>5</v>
-      </c>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>А115</t>
+          <t>А-653</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1556,7 +1550,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1564,21 +1558,29 @@
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Голубев М.Г.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>А-612</t>
+          <t>ПА-519</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1587,7 +1589,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1603,38 +1605,34 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>А228</t>
+          <t>А-367</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>22 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -1644,16 +1642,16 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>А771</t>
+          <t>ГУ-558</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Актовый зал</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>28</v>
+        <v>5000</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1662,24 +1660,24 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ПК (7 шт), TV</t>
+          <t>Господь порядок разводить изучить приятель.</t>
         </is>
       </c>
       <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>А-612</t>
+          <t>А435</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1688,7 +1686,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1697,99 +1695,93 @@
       </c>
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ЦИТ-470</t>
+          <t>ГУ-115</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>22 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>А-910</t>
+          <t>ПА-351</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Спортивный зал</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Покидать военный пробовать коробка бабочка прелесть.</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>2</v>
-      </c>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ЛК138</t>
+          <t>А271</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Спортивный зал</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1797,21 +1789,25 @@
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Селезнева Н.И.</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ГУ-115</t>
+          <t>ЛК343</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1820,19 +1816,31 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Хлеб каюта степь табак вытаскивать понятный.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Кулаков Т.Х.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -1842,12 +1850,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ГУ-515</t>
+          <t>ЛК-778</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -1858,20 +1866,30 @@
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>24 ПК, TV</t>
+        </is>
+      </c>
       <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>А-718</t>
+          <t>ЦИТ-134</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1880,7 +1898,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1891,31 +1909,31 @@
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Институт экономики и финансов</t>
+          <t>Институт маркетинга</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ГУ-574</t>
+          <t>ЦИТ-134</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1924,27 +1942,33 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ставить торговля прежний интеллектуальный.</t>
+          <t>17 ПК, TV</t>
         </is>
       </c>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ГУ-437</t>
+          <t>ЛК867</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -1955,22 +1979,26 @@
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>21 ПК, TV</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ЛК-721</t>
+          <t>ГУ-499</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1979,7 +2007,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>48</v>
+        <v>132</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1987,56 +2015,58 @@
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Дорофеева А.Д.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
           <t>Главный учебный корпус</t>
         </is>
       </c>
-      <c r="I48" t="n">
-        <v>5</v>
-      </c>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>А771</t>
+          <t>ГУ-558</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Моноблок (6 шт), TV</t>
-        </is>
-      </c>
+      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ЦИТ-821</t>
+          <t>ЛК-509</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2045,27 +2075,37 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Войти пол сынок факультет стакан дремать.</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ПА-835</t>
+          <t>А731</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2074,7 +2114,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2083,36 +2123,44 @@
       </c>
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ПА-272</t>
+          <t>ЦИТ-771</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>21 ПК, TV</t>
+        </is>
+      </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
@@ -2120,45 +2168,47 @@
           <t>Главный учебный корпус</t>
         </is>
       </c>
-      <c r="I52" t="n">
-        <v>3</v>
-      </c>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ЛК408</t>
+          <t>ГУ-473</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>21 ПК, TV</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ЛК242</t>
+          <t>ЛК-509</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2167,7 +2217,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2183,13 +2233,13 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ЛК-721</t>
+          <t>ПА-351</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2198,7 +2248,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>70</v>
+        <v>192</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2207,127 +2257,121 @@
       </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
           <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>А868</t>
+          <t>ЦИТ-252</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Моноблок (14 шт), экран</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Институт экономики и финансов</t>
-        </is>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ЦИТ-140</t>
+          <t>А-224</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Моноблок (14 шт), TV</t>
+        </is>
+      </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ГУ-115</t>
+          <t>ЦИТ-134</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Моноблок (8 шт), экран</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ЛК567</t>
+          <t>ГУ530</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2336,7 +2380,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -2344,64 +2388,56 @@
         </is>
       </c>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Лаврентьева Л.В.</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ГУ-744</t>
+          <t>ЛК374</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Дистанционное проведение</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Дрогнуть мальчишка еврейский постоянный.</t>
-        </is>
-      </c>
+      <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
           <t>Административный корпус</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ГУ633</t>
+          <t>ЛК-509</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2410,15 +2446,23 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Деньги танцевать возмутиться тута деловой район труп.</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Капустина М.Я.</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
@@ -2426,57 +2470,57 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ПА-922</t>
+          <t>ЛК-989</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>192</v>
+        <v>16</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Галкин В.Б.</t>
-        </is>
-      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>17 ПК, TV</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ЛК549</t>
+          <t>ГУ-638</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Спортивный зал</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>400</v>
+        <v>60</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2488,15 +2532,17 @@
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ГУ-618</t>
+          <t>А731</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2505,38 +2551,50 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Сохранять эффект коммунизм соответствие затянуться разуметься пропасть.</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Карпова С.Е.</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ПА-716</t>
+          <t>ЛК-225</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Спортивный зал</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>400</v>
+        <v>60</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2545,18 +2603,24 @@
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ЛК237</t>
+          <t>А380</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2565,7 +2629,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>28</v>
+        <v>200</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2577,17 +2641,17 @@
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ГУ-618</t>
+          <t>А271</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2596,7 +2660,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -2605,66 +2669,64 @@
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Институт экономики и финансов</t>
-        </is>
-      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ЛК179</t>
+          <t>ПА-494</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Общего назначения</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>ПК (9 шт), TV</t>
-        </is>
-      </c>
+      <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ПА-403</t>
+          <t>ЛК512</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Дистанционное проведение</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -2676,96 +2738,112 @@
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I69" t="n">
-        <v>6</v>
-      </c>
+          <t>Лабораторный корпус</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>А-349</t>
+          <t>ЦИТ-781</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>22 ПК, TV</t>
+        </is>
+      </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I70" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>А-826</t>
+          <t>ПА-175</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>24</v>
+        <v>132</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>Моноблок (8 шт), экран</t>
-        </is>
-      </c>
+      <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
+          <t>ПА-524</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Учебная аудитория</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>176</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Государственный университет управления</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr"/>
       <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ЦИТ-724</t>
+          <t>ЛК614</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2774,7 +2852,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -2783,28 +2861,24 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Непривычный степь военный степь низкий приятель выбирать.</t>
+          <t>Совет изба металл инструкция.</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+      <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I73" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ЛК-315</t>
+          <t>ЛК531</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2813,29 +2887,33 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>А дошлый поговорить аллея актриса невыносимый.</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I74" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>А-741</t>
+          <t>ЛК383</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2844,7 +2922,7 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -2856,88 +2934,96 @@
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ГУ-437</t>
+          <t>ЦИТ-252</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Моноблок (7 шт), TV</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>А-409</t>
+          <t>ПА-175</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>Моноблок (12 шт), TV</t>
-        </is>
-      </c>
+      <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>А-849</t>
+          <t>А-591</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -2946,28 +3032,24 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>10 ПК, TV</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>Мельников Т.Т.</t>
-        </is>
-      </c>
+          <t>Вскинуть падаль правильный руководитель возмутиться.</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I78" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>А368</t>
+          <t>ПА-519</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2976,7 +3058,7 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>176</v>
+        <v>200</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -2988,26 +3070,26 @@
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ЛК-919</t>
+          <t>ЛК-948</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -3016,59 +3098,63 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Наслаждение пропадать сынок.</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr"/>
+          <t>24 ПК, TV</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Комаров В.Б.</t>
+        </is>
+      </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
           <t>Административный корпус</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ЛК-189</t>
+          <t>ЛК557</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>ПК (13 шт), TV</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Якушева П.В.</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>Лабораторный корпус</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ПА-575</t>
+          <t>ПА-189</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3077,38 +3163,42 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Терапия дошлый прежний применяться.</t>
+        </is>
+      </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ПА-220</t>
+          <t>ЛК890</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -3117,24 +3207,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Господь табак подробность плясать термин пространство дальний.</t>
+          <t>10 ПК, TV</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ГУ-415</t>
+          <t>ГУ169</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3143,7 +3233,7 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -3154,12 +3244,12 @@
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Институт экономики и финансов</t>
+          <t>Институт маркетинга</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I84" t="n">
@@ -3169,61 +3259,77 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
+          <t>ГУ689</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Компьютерный класс</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>25</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Государственный университет управления</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>18 ПК, TV</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Ильина С.И.</t>
+        </is>
+      </c>
       <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ПА-672</t>
+          <t>ГУ825</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>12 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E86" t="inlineStr"/>
       <c r="F86" t="inlineStr"/>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+      <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ПА-220</t>
+          <t>ПА-764</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3232,7 +3338,7 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -3244,17 +3350,17 @@
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ПА-524</t>
+          <t>ЛК223</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3275,26 +3381,26 @@
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ПА-922</t>
+          <t>ЛК454</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Общего назначения</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -3306,50 +3412,50 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I89" t="n">
-        <v>7</v>
-      </c>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>А-718</t>
+          <t>ПА-588</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>25</v>
+        <v>200</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>14 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E90" t="inlineStr"/>
       <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>А946</t>
+          <t>ЛК383</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3358,7 +3464,7 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>50</v>
+        <v>176</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -3367,18 +3473,24 @@
       </c>
       <c r="E91" t="inlineStr"/>
       <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ГУ-515</t>
+          <t>А-224</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3387,7 +3499,7 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>132</v>
+        <v>200</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -3396,51 +3508,39 @@
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H92" t="inlineStr">
         <is>
           <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ЛК374</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Учебная аудитория</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>48</v>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Государственный университет управления</t>
-        </is>
-      </c>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I93" t="n">
-        <v>8</v>
-      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ПА-224</t>
+          <t>ЛК-989</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3449,7 +3549,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -3459,13 +3559,13 @@
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Котов Г.И.</t>
+          <t>Щукин К.А.</t>
         </is>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I94" t="n">
@@ -3475,16 +3575,16 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>А-849</t>
+          <t>А-505</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -3492,25 +3592,25 @@
         </is>
       </c>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Калашникова Л.Д.</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ЦИТ-533</t>
+          <t>А-367</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3519,7 +3619,7 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -3528,28 +3628,24 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>18 ПК, TV</t>
+          <t>19 ПК, TV</t>
         </is>
       </c>
       <c r="F96" t="inlineStr"/>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Институт экономики и финансов</t>
-        </is>
-      </c>
+      <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ПА-220</t>
+          <t>А731</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3558,7 +3654,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -3566,30 +3662,38 @@
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Осипов Э.Б.</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ПА-124</t>
+          <t>ЛК-324</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -3598,24 +3702,28 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>20 ПК, TV</t>
+          <t>Моноблок (6 шт), проектор</t>
         </is>
       </c>
       <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ГУ351</t>
+          <t>ЦИТ-435</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3624,23 +3732,15 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Нож куча тюрьма похороны рассуждение рис.</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>Ларионова И.Ф.</t>
-        </is>
-      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
           <t>Институт информационных систем</t>
@@ -3648,7 +3748,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -3656,38 +3756,22 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>А946</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Общего назначения</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>30</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Государственный университет управления</t>
-        </is>
-      </c>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr"/>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="I100" t="n">
-        <v>4</v>
-      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ЛК780</t>
+          <t>ГУ-554</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3696,7 +3780,7 @@
         </is>
       </c>
       <c r="C101" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -3708,7 +3792,7 @@
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I101" t="n">
@@ -3718,7 +3802,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ЛК-942</t>
+          <t>А116</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3727,7 +3811,7 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -3735,34 +3819,56 @@
         </is>
       </c>
       <c r="E102" t="inlineStr"/>
-      <c r="F102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Громов В.В.</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>Лабораторный корпус</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr"/>
-      <c r="C103" t="inlineStr"/>
-      <c r="D103" t="inlineStr"/>
+          <t>ГУ187</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Учебная аудитория</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>26</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Государственный университет управления</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr"/>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr"/>
-      <c r="H103" t="inlineStr"/>
-      <c r="I103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>А-910</t>
+          <t>ГУ-804</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3771,7 +3877,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -3780,33 +3886,33 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>20 ПК, TV</t>
+          <t>14 ПК, TV</t>
         </is>
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ГУ780</t>
+          <t>А-284</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Актовый зал</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -3818,26 +3924,26 @@
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>А-674</t>
+          <t>ГУ-473</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Дистанционное проведение</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -3848,38 +3954,42 @@
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Институт экономики и финансов</t>
+          <t>Институт информационных систем</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>А368</t>
+          <t>ГУ187</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>200</v>
+        <v>30</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>10 ПК, TV</t>
+        </is>
+      </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
@@ -3887,12 +3997,14 @@
           <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
+      <c r="I107" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ПА-500</t>
+          <t>А-388</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3908,46 +4020,36 @@
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Вперед сбросить прелесть порода постоянный пропадать.</t>
-        </is>
-      </c>
+      <c r="E108" t="inlineStr"/>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I108" t="n">
-        <v>4</v>
-      </c>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ЦИТ-813</t>
+          <t>ГУ-350</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>24 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E109" t="inlineStr"/>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
@@ -3962,22 +4064,38 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr"/>
-      <c r="C110" t="inlineStr"/>
-      <c r="D110" t="inlineStr"/>
+          <t>ЛК223</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Учебная аудитория</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>38</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Государственный университет управления</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
-      <c r="I110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>А603</t>
+          <t>ПА-519</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3986,7 +4104,7 @@
         </is>
       </c>
       <c r="C111" t="n">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -3998,22 +4116,22 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ЛК857</t>
+          <t>ГУ853</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -4024,68 +4142,62 @@
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>17 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E112" t="inlineStr"/>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Институт экономики и финансов</t>
+          <t>Институт маркетинга</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ЛК903</t>
+          <t>ГУ-499</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Спортивный зал</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>400</v>
+        <v>48</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Похороны неожиданный некоторый что приятель.</t>
-        </is>
-      </c>
+      <c r="E113" t="inlineStr"/>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ПА-716</t>
+          <t>ЛК557</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -4098,7 +4210,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Моноблок (14 шт), проектор</t>
+          <t>25 ПК, TV</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -4109,13 +4221,13 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ГУ-574</t>
+          <t>ЛК606</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4124,7 +4236,7 @@
         </is>
       </c>
       <c r="C115" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -4132,8 +4244,16 @@
         </is>
       </c>
       <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr"/>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Бирюкова П.Б.</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H115" t="inlineStr">
         <is>
           <t>Поточный корпус</t>
@@ -4144,7 +4264,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ЦИТ-228</t>
+          <t>ЛК824</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4153,7 +4273,7 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>200</v>
+        <v>26</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -4169,17 +4289,17 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ГУ-846</t>
+          <t>ЦИТ-247</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4188,7 +4308,7 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -4197,24 +4317,24 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Моноблок (8 шт), TV</t>
+          <t>Моноблок (14 шт), экран</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>А-322</t>
+          <t>А467</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4223,50 +4343,54 @@
         </is>
       </c>
       <c r="C118" t="n">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Мусор темнеть вывести ставить.</t>
+        </is>
+      </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I118" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ЛК111</t>
+          <t>ЛК-570</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>10 ПК, TV</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Некрасова Ю.А.</t>
+        </is>
+      </c>
       <c r="G119" t="inlineStr"/>
       <c r="H119" t="inlineStr">
         <is>
@@ -4274,13 +4398,13 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ЦИТ-634</t>
+          <t>ЛК-570</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4289,7 +4413,7 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -4300,29 +4424,31 @@
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Институт управления</t>
+          <t>Институт экономики и финансов</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="I120" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ПА-835</t>
+          <t>А467</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -4331,7 +4457,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>ПК (9 шт), экран</t>
+          <t>13 ПК, TV</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
@@ -4342,13 +4468,13 @@
         </is>
       </c>
       <c r="I121" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ПА-500</t>
+          <t>ГУ-115</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4357,7 +4483,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -4369,17 +4495,17 @@
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ЦИТ-533</t>
+          <t>ЛК-581</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4388,7 +4514,7 @@
         </is>
       </c>
       <c r="C123" t="n">
-        <v>28</v>
+        <v>176</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -4400,63 +4526,61 @@
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I123" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ГУ-415</t>
+          <t>ГУ-499</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>Засунуть низкий вчера.</t>
-        </is>
-      </c>
+      <c r="E124" t="inlineStr"/>
       <c r="F124" t="inlineStr"/>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Институт информационных систем</t>
+          <t>Институт управления</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ПА-701</t>
+          <t>ЛК-932</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -4465,33 +4589,27 @@
       </c>
       <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Институт экономики и финансов</t>
-        </is>
-      </c>
+      <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="I125" t="n">
-        <v>1</v>
-      </c>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>А600</t>
+          <t>ЛК497</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -4500,90 +4618,88 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Функция столетие вскакивать тревога передо бабочка.</t>
+          <t>10 ПК, TV</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I126" t="n">
-        <v>1</v>
-      </c>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ЛК790</t>
+          <t>ЛК-497</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>13 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E127" t="inlineStr"/>
       <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Институт экономики и финансов</t>
-        </is>
-      </c>
+      <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
           <t>Административный корпус</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr"/>
+      <c r="I127" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ПА-220</t>
+          <t>ЛК-824</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Дистанционное проведение</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>19 ПК, TV</t>
+        </is>
+      </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr"/>
+          <t>Цифровой корпус ГУУ</t>
+        </is>
+      </c>
+      <c r="I128" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>А-639</t>
+          <t>ПА-535</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4600,61 +4716,61 @@
         </is>
       </c>
       <c r="E129" t="inlineStr"/>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Яковлев М.А.</t>
-        </is>
-      </c>
+      <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>А-309</t>
+          <t>А-860</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Спортивный зал</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>400</v>
+        <v>24</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Освобождение житель снимать вчера.</t>
+        </is>
+      </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ЛК990</t>
+          <t>ПА-836</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -4665,26 +4781,26 @@
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>20 ПК, TV</t>
+        </is>
+      </c>
       <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I131" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ЛК790</t>
+          <t>ЛК-553</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4693,7 +4809,7 @@
         </is>
       </c>
       <c r="C132" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -4705,17 +4821,17 @@
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ГУ840</t>
+          <t>ПА-384</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4724,7 +4840,7 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -4735,20 +4851,22 @@
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Институт управления</t>
+          <t>Институт экономики и финансов</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr"/>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I133" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ЦИТ-253</t>
+          <t>ЛК454</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4757,38 +4875,42 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>192</v>
+        <v>38</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Ягода низкий снимать.</t>
+        </is>
+      </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I134" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ПА-922</t>
+          <t>ЦИТ-252</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -4797,14 +4919,18 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>14 ПК, TV</t>
+          <t>Миг вряд невозможно идея спешить райком.</t>
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I135" t="n">
@@ -4814,16 +4940,16 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>А413</t>
+          <t>ЛК-404</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Общего назначения</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -4832,10 +4958,14 @@
       </c>
       <c r="E136" t="inlineStr"/>
       <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I136" t="n">
@@ -4845,7 +4975,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ЛК242</t>
+          <t>ПА-728</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4854,7 +4984,7 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>176</v>
+        <v>48</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -4863,18 +4993,24 @@
       </c>
       <c r="E137" t="inlineStr"/>
       <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr"/>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="I137" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ГУ209</t>
+          <t>ЛК-831</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4883,7 +5019,7 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -4891,48 +5027,54 @@
         </is>
       </c>
       <c r="E138" t="inlineStr"/>
-      <c r="F138" t="inlineStr"/>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Григорьева Л.Е.</t>
+        </is>
+      </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Институт информационных систем</t>
+          <t>Институт маркетинга</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I138" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ПА-524</t>
+          <t>ПА-189</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Актовый зал</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Моноблок (14 шт), TV</t>
+        </is>
+      </c>
       <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I139" t="n">
@@ -4942,7 +5084,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ЛК796</t>
+          <t>ПА-528</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4951,7 +5093,7 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -4963,7 +5105,7 @@
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I140" t="n">
@@ -4973,7 +5115,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>А644</t>
+          <t>ЛК255</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4998,13 +5140,13 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ПА-922</t>
+          <t>ПА-519</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5013,7 +5155,7 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -5025,17 +5167,17 @@
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ЦИТ-575</t>
+          <t>ГУ570</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5044,7 +5186,7 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -5053,10 +5195,14 @@
       </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" t="inlineStr"/>
-      <c r="G143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I143" t="n">
@@ -5066,16 +5212,16 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ГУ924</t>
+          <t>ЛК223</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Спортивный зал</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>26</v>
+        <v>400</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -5084,24 +5230,20 @@
       </c>
       <c r="E144" t="inlineStr"/>
       <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ЛК374</t>
+          <t>ПА-588</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5110,7 +5252,7 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>200</v>
+        <v>38</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -5119,20 +5261,24 @@
       </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" t="inlineStr"/>
-      <c r="G145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>А314</t>
+          <t>ГУ-638</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5141,16 +5287,28 @@
         </is>
       </c>
       <c r="C146" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr"/>
-      <c r="F146" t="inlineStr"/>
-      <c r="G146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Посидеть пол выразить смертельный.</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Федотов И.М.</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H146" t="inlineStr">
         <is>
           <t>Поточный корпус</t>
@@ -5163,16 +5321,16 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ПА-102</t>
+          <t>ГУ304</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Актовый зал</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>800</v>
+        <v>26</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -5181,49 +5339,59 @@
       </c>
       <c r="E147" t="inlineStr"/>
       <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I147" t="inlineStr"/>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I147" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ЛК990</t>
+          <t>ЛК784</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>132</v>
+        <v>15</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>17 ПК, TV</t>
+        </is>
+      </c>
       <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ГУ209</t>
+          <t>ЛК-778</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5232,7 +5400,7 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -5241,24 +5409,24 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>23 ПК, TV</t>
+          <t>17 ПК, TV</t>
         </is>
       </c>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ПА-412</t>
+          <t>ЛК-324</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5267,7 +5435,7 @@
         </is>
       </c>
       <c r="C150" t="n">
-        <v>100</v>
+        <v>176</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -5279,7 +5447,7 @@
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I150" t="n">
@@ -5289,114 +5457,102 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>А-910</t>
+          <t>ГУ205</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>11 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E151" t="inlineStr"/>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+      <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr"/>
+          <t>Лабораторный корпус</t>
+        </is>
+      </c>
+      <c r="I151" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ПА-124</t>
+          <t>А-873</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>21 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ЦИТ-821</t>
+          <t>ЛК606</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>15 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E153" t="inlineStr"/>
       <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I153" t="n">
-        <v>7</v>
-      </c>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ПА-922</t>
+          <t>ГУ217</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5405,29 +5561,37 @@
         </is>
       </c>
       <c r="C154" t="n">
-        <v>28</v>
+        <v>132</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Человечек обида важный заработать.</t>
+        </is>
+      </c>
       <c r="F154" t="inlineStr"/>
-      <c r="G154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I154" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ЛК378</t>
+          <t>А-388</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5436,7 +5600,7 @@
         </is>
       </c>
       <c r="C155" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -5444,63 +5608,63 @@
         </is>
       </c>
       <c r="E155" t="inlineStr"/>
-      <c r="F155" t="inlineStr"/>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Дьячков А.И.</t>
+        </is>
+      </c>
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
-      <c r="I155" t="n">
-        <v>5</v>
-      </c>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>А-650</t>
+          <t>ЛК890</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>24 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E156" t="inlineStr"/>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I156" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ЦИТ-255</t>
+          <t>А-367</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -5509,22 +5673,28 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>ПК (8 шт), экран</t>
+          <t>15 ПК, TV</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
-      <c r="G157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr"/>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I157" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ГУ-389</t>
+          <t>ПА-126</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5533,7 +5703,7 @@
         </is>
       </c>
       <c r="C158" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -5542,94 +5712,64 @@
       </c>
       <c r="E158" t="inlineStr"/>
       <c r="F158" t="inlineStr"/>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+      <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I158" t="n">
-        <v>2</v>
-      </c>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>А-805</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Общего назначения</t>
-        </is>
-      </c>
-      <c r="C159" t="n">
-        <v>16</v>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Государственный университет управления</t>
-        </is>
-      </c>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr"/>
       <c r="F159" t="inlineStr"/>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I159" t="n">
-        <v>2</v>
-      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ГУ-846</t>
+          <t>ЛК993</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>10 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E160" t="inlineStr"/>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ПА-846</t>
+          <t>ЦИТ-781</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5638,27 +5778,33 @@
         </is>
       </c>
       <c r="C161" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Сынок радость прошептать каюта очередной.</t>
+        </is>
+      </c>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I161" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ПА-102</t>
+          <t>А435</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5667,7 +5813,7 @@
         </is>
       </c>
       <c r="C162" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -5679,17 +5825,15 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I162" t="n">
-        <v>4</v>
-      </c>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ГУ-846</t>
+          <t>ЛК-324</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5698,7 +5842,7 @@
         </is>
       </c>
       <c r="C163" t="n">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -5710,52 +5854,48 @@
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ЛК242</t>
+          <t>ЛК-389</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>14</v>
+        <v>200</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>11 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E164" t="inlineStr"/>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ПА-224</t>
+          <t>ГУ205</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5764,7 +5904,7 @@
         </is>
       </c>
       <c r="C165" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -5773,37 +5913,31 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>ПК (14 шт), экран</t>
+          <t>ПК (6 шт), экран</t>
         </is>
       </c>
       <c r="F165" t="inlineStr"/>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
-      <c r="I165" t="n">
-        <v>1</v>
-      </c>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ЦИТ-491</t>
+          <t>ЛК-833</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Актовый зал</t>
         </is>
       </c>
       <c r="C166" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -5812,24 +5946,18 @@
       </c>
       <c r="E166" t="inlineStr"/>
       <c r="F166" t="inlineStr"/>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>Институт экономики и финансов</t>
-        </is>
-      </c>
+      <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I166" t="n">
-        <v>8</v>
-      </c>
+          <t>Спортивный комплекс</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>А644</t>
+          <t>А435</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5838,7 +5966,7 @@
         </is>
       </c>
       <c r="C167" t="n">
-        <v>30</v>
+        <v>176</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -5850,7 +5978,7 @@
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I167" t="n">
@@ -5860,22 +5988,42 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr"/>
-      <c r="C168" t="inlineStr"/>
-      <c r="D168" t="inlineStr"/>
+          <t>ПА-530</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Учебная аудитория</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>38</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Государственный университет управления</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
-      <c r="G168" t="inlineStr"/>
-      <c r="H168" t="inlineStr"/>
-      <c r="I168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I168" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ПА-370</t>
+          <t>ПА-515</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5884,23 +6032,23 @@
         </is>
       </c>
       <c r="C169" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Жестокий покинуть миллиард.</t>
+        </is>
+      </c>
       <c r="F169" t="inlineStr"/>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>Институт экономики и финансов</t>
-        </is>
-      </c>
+      <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -5908,28 +6056,28 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>А-718</t>
+          <t>ЛК-570</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C170" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>Панова М.Ю.</t>
-        </is>
-      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>11 ПК, TV</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
@@ -5943,23 +6091,27 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>ПА-922</t>
+          <t>ЛК993</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C171" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>23 ПК, TV</t>
+        </is>
+      </c>
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
@@ -5967,12 +6119,14 @@
           <t>Главный учебный корпус</t>
         </is>
       </c>
-      <c r="I171" t="inlineStr"/>
+      <c r="I171" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ЛК374</t>
+          <t>ЛК993</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5981,7 +6135,7 @@
         </is>
       </c>
       <c r="C172" t="n">
-        <v>132</v>
+        <v>20</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -5990,22 +6144,20 @@
       </c>
       <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr"/>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr"/>
+          <t>Главный учебный корпус</t>
+        </is>
+      </c>
+      <c r="I172" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>А314</t>
+          <t>ЛК-553</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -6014,7 +6166,7 @@
         </is>
       </c>
       <c r="C173" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -6026,15 +6178,17 @@
       <c r="G173" t="inlineStr"/>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I173" t="inlineStr"/>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I173" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>ГУ780</t>
+          <t>ГУ-350</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6043,7 +6197,7 @@
         </is>
       </c>
       <c r="C174" t="n">
-        <v>30</v>
+        <v>132</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -6055,26 +6209,26 @@
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I174" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>ГУ-415</t>
+          <t>ЛК-824</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C175" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -6083,66 +6237,72 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>16 ПК, TV</t>
+          <t>Избегать возникновение дурацкий выдержать.</t>
         </is>
       </c>
       <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Институт информационных систем</t>
+          <t>Институт экономики и финансов</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr"/>
+          <t>Центр информационных технологий (БЦ)</t>
+        </is>
+      </c>
+      <c r="I175" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>ПА-716</t>
+          <t>ЛК-449</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C176" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>14 ПК, TV</t>
+        </is>
+      </c>
       <c r="F176" t="inlineStr"/>
       <c r="G176" t="inlineStr"/>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I176" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>ПА-524</t>
+          <t>А435</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C177" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -6150,11 +6310,7 @@
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>Фомина Л.А.</t>
-        </is>
-      </c>
+      <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
@@ -6162,34 +6318,38 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ГУ-115</t>
+          <t>ЛК-778</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C178" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>18 ПК, TV</t>
+        </is>
+      </c>
       <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I178" t="n">
@@ -6199,16 +6359,16 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ЛК408</t>
+          <t>ЛК454</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Дистанционное проведение</t>
         </is>
       </c>
       <c r="C179" t="n">
-        <v>100</v>
+        <v>5000</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -6216,69 +6376,69 @@
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>Ковалева Э.Р.</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Институт управления</t>
+        </is>
+      </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I179" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ЛК242</t>
+          <t>ГУ-498</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C180" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>22 ПК, TV</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Зайцева В.Ф.</t>
+        </is>
+      </c>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I180" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ЛК790</t>
+          <t>ГУ593</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Дистанционное проведение</t>
         </is>
       </c>
       <c r="C181" t="n">
-        <v>70</v>
+        <v>5000</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -6287,11 +6447,7 @@
       </c>
       <c r="E181" t="inlineStr"/>
       <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+      <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr">
         <is>
           <t>Цифровой корпус ГУУ</t>
@@ -6304,38 +6460,46 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ЦИТ-897</t>
+          <t>ГУ400</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Актовый зал</t>
         </is>
       </c>
       <c r="C182" t="n">
-        <v>192</v>
+        <v>800</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Мелькнуть руководитель актриса налево около.</t>
+        </is>
+      </c>
       <c r="F182" t="inlineStr"/>
-      <c r="G182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I182" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ГУ351</t>
+          <t>ПА-358</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6344,7 +6508,7 @@
         </is>
       </c>
       <c r="C183" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -6353,67 +6517,63 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>ПК (5 шт), проектор</t>
+          <t>Моноблок (11 шт), проектор</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Тихонова Т.С.</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
+          <t>Гаврилова К.А.</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I183" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ЛК179</t>
+          <t>ЛК557</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Лаборатория</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C184" t="n">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>ПК (8 шт), проектор</t>
-        </is>
-      </c>
+      <c r="E184" t="inlineStr"/>
       <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Институт маркетинга</t>
+        </is>
+      </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I184" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ЦИТ-126</t>
+          <t>ГУ187</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6422,7 +6582,7 @@
         </is>
       </c>
       <c r="C185" t="n">
-        <v>132</v>
+        <v>48</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -6434,24 +6594,26 @@
       <c r="G185" t="inlineStr"/>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Поточный корпус</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I185" t="n">
+        <v>6</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ЛК138</t>
+          <t>ГУ304</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Дистанционное проведение</t>
         </is>
       </c>
       <c r="C186" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -6463,48 +6625,52 @@
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>А-978</t>
+          <t>ГУ463</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C187" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>21 ПК, TV</t>
+        </is>
+      </c>
       <c r="F187" t="inlineStr"/>
       <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I187" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ГУ667</t>
+          <t>А-860</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6513,72 +6679,58 @@
         </is>
       </c>
       <c r="C188" t="n">
-        <v>132</v>
+        <v>36</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Успокоиться адвокат издали армейский бегать.</t>
-        </is>
-      </c>
+      <c r="E188" t="inlineStr"/>
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I188" t="n">
-        <v>8</v>
-      </c>
+          <t>Лабораторный корпус</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ГУ-958</t>
+          <t>ЛК-932</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C189" t="n">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>12 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E189" t="inlineStr"/>
       <c r="F189" t="inlineStr"/>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I189" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>А-718</t>
+          <t>ЛК824</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6587,7 +6739,7 @@
         </is>
       </c>
       <c r="C190" t="n">
-        <v>176</v>
+        <v>24</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -6596,24 +6748,20 @@
       </c>
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Институт маркетинга</t>
-        </is>
-      </c>
+      <c r="G190" t="inlineStr"/>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I190" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ЦИТ-253</t>
+          <t>ГУ593</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6622,68 +6770,64 @@
         </is>
       </c>
       <c r="C191" t="n">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>Актриса один одиннадцать костер.</t>
-        </is>
-      </c>
+      <c r="E191" t="inlineStr"/>
       <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Институт экономики и финансов</t>
+        </is>
+      </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I191" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ЦИТ-634</t>
+          <t>А-505</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C192" t="n">
-        <v>16</v>
+        <v>200</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>13 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E192" t="inlineStr"/>
       <c r="F192" t="inlineStr"/>
       <c r="G192" t="inlineStr"/>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Цифровой корпус ГУУ</t>
+          <t>Поточный корпус</t>
         </is>
       </c>
       <c r="I192" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>А946</t>
+          <t>А154</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6692,7 +6836,7 @@
         </is>
       </c>
       <c r="C193" t="n">
-        <v>192</v>
+        <v>50</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -6704,15 +6848,17 @@
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="I193" t="inlineStr"/>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ЛК865</t>
+          <t>ЦИТ-879</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6721,7 +6867,7 @@
         </is>
       </c>
       <c r="C194" t="n">
-        <v>176</v>
+        <v>38</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -6733,17 +6879,17 @@
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I194" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ЛК780</t>
+          <t>ЛК-324</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6752,7 +6898,7 @@
         </is>
       </c>
       <c r="C195" t="n">
-        <v>176</v>
+        <v>70</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -6764,7 +6910,7 @@
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Лабораторный корпус</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -6772,7 +6918,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ЛК-988</t>
+          <t>ЛК784</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6781,7 +6927,7 @@
         </is>
       </c>
       <c r="C196" t="n">
-        <v>50</v>
+        <v>176</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -6789,19 +6935,25 @@
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Колобов П.И.</t>
+        </is>
+      </c>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr"/>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I196" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>А644</t>
+          <t>ЦИТ-406</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6810,7 +6962,7 @@
         </is>
       </c>
       <c r="C197" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -6818,61 +6970,69 @@
         </is>
       </c>
       <c r="E197" t="inlineStr"/>
-      <c r="F197" t="inlineStr"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Воронов Ф.В.</t>
+        </is>
+      </c>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
+          <t>Административный корпус</t>
+        </is>
+      </c>
+      <c r="I197" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>А-309</t>
+          <t>ЛК-178</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C198" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>22 ПК, TV</t>
+        </is>
+      </c>
       <c r="F198" t="inlineStr"/>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr"/>
+          <t>Поточный корпус</t>
+        </is>
+      </c>
+      <c r="I198" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ГУ359</t>
+          <t>А-591</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Лаборатория</t>
         </is>
       </c>
       <c r="C199" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -6881,59 +7041,55 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>22 ПК, TV</t>
+          <t>Моноблок (13 шт), проектор</t>
         </is>
       </c>
       <c r="F199" t="inlineStr"/>
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
+          <t>Цифровой корпус ГУУ</t>
         </is>
       </c>
       <c r="I199" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ГУ860</t>
+          <t>ГУ260</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C200" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>20 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E200" t="inlineStr"/>
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Спортивный комплекс</t>
+          <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I200" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>ПА-309</t>
+          <t>ЛК-948</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6942,7 +7098,7 @@
         </is>
       </c>
       <c r="C201" t="n">
-        <v>36</v>
+        <v>176</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -6951,64 +7107,64 @@
       </c>
       <c r="E201" t="inlineStr"/>
       <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Институт информационных систем</t>
+        </is>
+      </c>
       <c r="H201" t="inlineStr">
         <is>
           <t>Главный учебный корпус</t>
         </is>
       </c>
       <c r="I201" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>А420</t>
+          <t>А-860</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Компьютерный класс</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C202" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>22 ПК, TV</t>
-        </is>
-      </c>
+      <c r="E202" t="inlineStr"/>
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Административный корпус</t>
         </is>
       </c>
       <c r="I202" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>А314</t>
+          <t>ГУ-638</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Общего назначения</t>
+          <t>Учебная аудитория</t>
         </is>
       </c>
       <c r="C203" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -7016,21 +7172,23 @@
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Зуев Д.А.</t>
+        </is>
+      </c>
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Административный корпус</t>
-        </is>
-      </c>
-      <c r="I203" t="n">
-        <v>7</v>
-      </c>
+          <t>Лабораторный корпус</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ЛК237</t>
+          <t>А775</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -7039,7 +7197,7 @@
         </is>
       </c>
       <c r="C204" t="n">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -7047,29 +7205,21 @@
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
-      <c r="F204" t="inlineStr">
-        <is>
-          <t>Тимофеева Е.О.</t>
-        </is>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>Институт информационных систем</t>
-        </is>
-      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Центр информационных технологий (БЦ)</t>
+          <t>Спортивный комплекс</t>
         </is>
       </c>
       <c r="I204" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ГУ962</t>
+          <t>ЛК-989</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -7078,7 +7228,7 @@
         </is>
       </c>
       <c r="C205" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -7090,7 +7240,7 @@
       <c r="G205" t="inlineStr"/>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Лабораторный корпус</t>
+          <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
       <c r="I205" t="n">
@@ -7100,135 +7250,36 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>А-349</t>
+          <t>ГУ-498</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Учебная аудитория</t>
+          <t>Компьютерный класс</t>
         </is>
       </c>
       <c r="C206" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
           <t>Государственный университет управления</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>14 ПК, TV</t>
+        </is>
+      </c>
       <c r="F206" t="inlineStr"/>
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Главный учебный корпус</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr"/>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>А420</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Учебная аудитория</t>
-        </is>
-      </c>
-      <c r="C207" t="n">
-        <v>60</v>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>Государственный университет управления</t>
-        </is>
-      </c>
-      <c r="E207" t="inlineStr"/>
-      <c r="F207" t="inlineStr"/>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>Институт управления</t>
-        </is>
-      </c>
-      <c r="H207" t="inlineStr">
-        <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I207" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>ПА-148</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Учебная аудитория</t>
-        </is>
-      </c>
-      <c r="C208" t="n">
-        <v>176</v>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>Государственный университет управления</t>
-        </is>
-      </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>Наступать космос заплакать развитый.</t>
-        </is>
-      </c>
-      <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr"/>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Цифровой корпус ГУУ</t>
-        </is>
-      </c>
-      <c r="I208" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>ЦИТ-575</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Компьютерный класс</t>
-        </is>
-      </c>
-      <c r="C209" t="n">
-        <v>27</v>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>Государственный университет управления</t>
-        </is>
-      </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>19 ПК, TV</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr"/>
-      <c r="G209" t="inlineStr"/>
-      <c r="H209" t="inlineStr">
-        <is>
           <t>Центр информационных технологий (БЦ)</t>
         </is>
       </c>
-      <c r="I209" t="n">
-        <v>5</v>
+      <c r="I206" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
